--- a/02-Task/English/English_Word_Ratings.xlsx
+++ b/02-Task/English/English_Word_Ratings.xlsx
@@ -108,8 +108,8 @@
     <t xml:space="preserve">w01_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **lightning**
- Please name all of the ways someone could use a **lightning**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **songbird**
+ Please name all of the ways someone could use a **songbird**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">01</t>
@@ -247,8 +247,8 @@
     <t xml:space="preserve">w02_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **sarcophagus**
- Please name all of the ways someone could use a **sarcophagus**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **bucktooth**
+ Please name all of the ways someone could use a **bucktooth**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">02</t>
@@ -296,8 +296,8 @@
     <t xml:space="preserve">w03_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **salon**
- Please name all of the ways someone could use a **salon**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **centrifuge**
+ Please name all of the ways someone could use a **centrifuge**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">03</t>
@@ -345,8 +345,8 @@
     <t xml:space="preserve">w04_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **watchtower**
- Please name all of the ways someone could use a **watchtower**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **town**
+ Please name all of the ways someone could use a **town**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">04</t>
@@ -394,8 +394,8 @@
     <t xml:space="preserve">w05_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **trident**
- Please name all of the ways someone could use a **trident**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **omelette**
+ Please name all of the ways someone could use a **omelette**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">05</t>
@@ -443,8 +443,8 @@
     <t xml:space="preserve">w06_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **flintstone**
- Please name all of the ways someone could use a **flintstone**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **orangutan**
+ Please name all of the ways someone could use a **orangutan**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">06</t>
@@ -492,8 +492,8 @@
     <t xml:space="preserve">w07_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **brig**
- Please name all of the ways someone could use a **brig**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **cub**
+ Please name all of the ways someone could use a **cub**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">07</t>
@@ -541,8 +541,8 @@
     <t xml:space="preserve">w08_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **park**
- Please name all of the ways someone could use a **park**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **millimeter**
+ Please name all of the ways someone could use a **millimeter**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">08</t>
@@ -590,8 +590,8 @@
     <t xml:space="preserve">w09_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **sloth**
- Please name all of the ways someone could use a **sloth**. Put one different use in each sloth.</t>
+    <t xml:space="preserve">### Word: **mansions**
+ Please name all of the ways someone could use a **mansions**. Put one different use in each mansions.</t>
   </si>
   <si>
     <t xml:space="preserve">09</t>
@@ -639,8 +639,8 @@
     <t xml:space="preserve">w10_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **excrement**
- Please name all of the ways someone could use a **excrement**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **firelight**
+ Please name all of the ways someone could use a **firelight**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">w10_use_01</t>

--- a/02-Task/English/English_Word_Ratings.xlsx
+++ b/02-Task/English/English_Word_Ratings.xlsx
@@ -108,8 +108,8 @@
     <t xml:space="preserve">w01_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **songbird**
- Please name all of the ways someone could use a **songbird**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **jewel**
+ Please name all of the ways someone could use a **jewel**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">01</t>
@@ -247,8 +247,8 @@
     <t xml:space="preserve">w02_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **bucktooth**
- Please name all of the ways someone could use a **bucktooth**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **crowd**
+ Please name all of the ways someone could use a **crowd**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">02</t>
@@ -296,8 +296,8 @@
     <t xml:space="preserve">w03_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **centrifuge**
- Please name all of the ways someone could use a **centrifuge**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **airport**
+ Please name all of the ways someone could use a **airport**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">03</t>
@@ -343,159 +343,159 @@
   </si>
   <si>
     <t xml:space="preserve">w04_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">### Word: **president**
+ Please name all of the ways someone could use a **president**. Put one different use in each box.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_more == 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_use_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w04_submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">### Word: **monkey**
+ Please name all of the ways someone could use a **monkey**. Put one different use in each box.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_more == 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_use_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w05_submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">### Word: **crack**
+ Please name all of the ways someone could use a **crack**. Put one different use in each box.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_more == 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_use_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w06_submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w07_prompt</t>
   </si>
   <si>
     <t xml:space="preserve">### Word: **town**
  Please name all of the ways someone could use a **town**. Put one different use in each box.</t>
   </si>
   <si>
-    <t xml:space="preserve">04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_more == 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_use_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w04_submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">### Word: **omelette**
- Please name all of the ways someone could use a **omelette**. Put one different use in each box.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_more == 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_use_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w05_submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">### Word: **orangutan**
- Please name all of the ways someone could use a **orangutan**. Put one different use in each box.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_more == 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_use_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w06_submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w07_prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">### Word: **cub**
- Please name all of the ways someone could use a **cub**. Put one different use in each box.</t>
-  </si>
-  <si>
     <t xml:space="preserve">07</t>
   </si>
   <si>
@@ -541,8 +541,8 @@
     <t xml:space="preserve">w08_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **millimeter**
- Please name all of the ways someone could use a **millimeter**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **room**
+ Please name all of the ways someone could use a **room**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">08</t>
@@ -590,8 +590,8 @@
     <t xml:space="preserve">w09_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **mansions**
- Please name all of the ways someone could use a **mansions**. Put one different use in each mansions.</t>
+    <t xml:space="preserve">### Word: **blackbird**
+ Please name all of the ways someone could use a **blackbird**. Put one different use in each blackbird.</t>
   </si>
   <si>
     <t xml:space="preserve">09</t>
@@ -639,8 +639,8 @@
     <t xml:space="preserve">w10_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">### Word: **firelight**
- Please name all of the ways someone could use a **firelight**. Put one different use in each box.</t>
+    <t xml:space="preserve">### Word: **fat**
+ Please name all of the ways someone could use a **fat**. Put one different use in each box.</t>
   </si>
   <si>
     <t xml:space="preserve">w10_use_01</t>
